--- a/Översikt ÖVERTORNEÅ.xlsx
+++ b/Översikt ÖVERTORNEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45813</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45403</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45705</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45586</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>45784</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>44635</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>45561</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45717</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>45136</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>46273</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>45288</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>45889</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45586</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>45127</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>45940</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
         <v>45096</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>46216</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
         <v>46093</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44880</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>45446</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>45017</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
         <v>45833</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>45833</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>45985</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>46206</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>45044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>44833</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>45462</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>46272</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>44833</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>44571</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>44587</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>44791</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>45197</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>46048</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>46171</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>45112</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>45807</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>45425</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>46269</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>45846</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>44585</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>44504</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5593,7 +5593,7 @@
         <v>44833</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>44494</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>44536</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>44864</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>44536</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>44553</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>44553</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44571</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44810</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         <v>44497</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>44581</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         <v>44553</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44557</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>44515</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         <v>44757</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         <v>44538</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         <v>44833</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>44687</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         <v>44557</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>44551</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44796</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7131,7 +7131,7 @@
         <v>44692</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>44662</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>44672</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         <v>44585</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7423,7 +7423,7 @@
         <v>44571</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>44816</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>45231</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>44692</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>45136</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>45576</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>45227</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>44797</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>45554</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45468</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>45673</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45622</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45622</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45377</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>44504</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>45142</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>44987</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8679,7 +8679,7 @@
         <v>45453</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         <v>45516</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8825,7 +8825,7 @@
         <v>45545</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>45573</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>45656</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>45602</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>45136</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>45136</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>45691</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>44910</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>45194</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44489</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>44671</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>45460</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>45274</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>45699</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>45395</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>45686</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>44748</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>45394</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>45750</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>45633</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>45632</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>44904</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>44553</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>44911</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>45691</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>45555</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>45407</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>45460</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>45390</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>45467</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>44860</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>45127</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>45827</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>45889</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>45894</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>45894</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>45894</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>45894</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>45589</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>45537</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>44589</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>45899</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>45633</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>45194</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>45684</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>45149</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>45547</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>45622</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>45621</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>45908</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>45727</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>46140</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>45910</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>45729</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>45910</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>46141</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>44914</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>46140</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>45504</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>46013</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>46057</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>45755</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>45919</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>46034</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>45575</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>45376</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>45926</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>45601</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>46142</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>45733</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>45932</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>45932</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>45932</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>45398</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>45936</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>45936</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>45938</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>44729</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>45574</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>45405</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>44917</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>45938</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14886,7 +14886,7 @@
         <v>45938</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14959,7 +14959,7 @@
         <v>44587</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>45451</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>45943</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>45940</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>45943</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>45946</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>45526</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>44635</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>45306</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>45959</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>45351</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
         <v>45118</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15845,7 +15845,7 @@
         <v>45961</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>45965</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>45965</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44930</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>45965</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>45965</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>45217</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>45772</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>45412</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>45167</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>46155</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45039</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45978</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45979</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>45979</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45979</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>45979</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>45559</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>45985</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>45435</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45982</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>45960</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>44529</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>45427</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>46160</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>46160</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>45273</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>46163</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>45995</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>46164</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>45996</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>46167</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>45743</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>46167</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>46003</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>46167</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>46167</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>46035</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>45589</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>46167</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>46167</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>46167</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>46003</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>45632</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>45632</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>46167</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>45857</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>45670</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>46008</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>46008</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>46008</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>46008</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>46010</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>45670</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>45281</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>45390</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>45700</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>45848</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>45460</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>46034</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>46034</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>46034</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>46034</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>46034</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>46032</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>46034</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>46034</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>46174</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>44776</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>46038</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>46038</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>46038</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>46038</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>46038</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>45686</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>44589</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>45685</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>46048</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>45467</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>45622</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>46178</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>46178</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>45667</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         <v>45351</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>46056</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>46057</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>45467</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>46058</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>46059</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>46059</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>44859</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>45104</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>46177</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>46059</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>46062</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>45092</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>46178</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         <v>46062</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>45685</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>46181</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>45887</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>46183</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>46181</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>45405</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>46182</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>45902</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>45639</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>46079</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>45139</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>46184</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>46080</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>46080</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>45792</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>45446</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>45509</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>45449</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>46185</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24416,7 +24416,7 @@
         <v>46185</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>46090</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>45377</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>46167</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>46094</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24781,7 +24781,7 @@
         <v>45188</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>45188</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>46094</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25000,7 +25000,7 @@
         <v>46094</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>45351</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>44601</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>46100</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>46104</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>45757</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>45953</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>46108</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>45574</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>46197</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>46108</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>45586</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         <v>45579</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>45329</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>45526</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26095,7 +26095,7 @@
         <v>46124</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>45364</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>45149</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>46129</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26387,7 +26387,7 @@
         <v>46246</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>46132</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>46246</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>44923</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>45772</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>45449</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>45632</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>45011</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>46246</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>45467</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>45112</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27190,7 +27190,7 @@
         <v>46251</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         <v>45602</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>45481</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27414,7 +27414,7 @@
         <v>46251</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>44532</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>45685</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>46162</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>45561</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>46210</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>45136</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>45117</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28008,7 +28008,7 @@
         <v>45516</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28081,7 +28081,7 @@
         <v>45595</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>46206</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>45870</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>46206</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>45775</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>44797</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28539,7 +28539,7 @@
         <v>46217</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>45017</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>45810</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>45685</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44634</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>46171</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>46136</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>44937</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         <v>46184</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>45515</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29284,7 +29284,7 @@
         <v>45418</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29357,7 +29357,7 @@
         <v>45707</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29430,7 +29430,7 @@
         <v>45727</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29503,7 +29503,7 @@
         <v>45379</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>46262</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>44672</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>46265</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>46108</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29868,7 +29868,7 @@
         <v>46267</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         <v>44484</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         <v>45300</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30087,7 +30087,7 @@
         <v>45629</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45520</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30233,7 +30233,7 @@
         <v>46267</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>46269</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>45467</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>46272</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>46231</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30603,7 +30603,7 @@
         <v>46272</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>46276</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>46277</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>45369</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30895,7 +30895,7 @@
         <v>45705</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>46274</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31041,7 +31041,7 @@
         <v>45602</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>45526</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>45393</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>46241</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>46241</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>46241</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31479,7 +31479,7 @@
         <v>46239</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>45137</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>45222</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>45799</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>45799</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>45602</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>46283</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>45139</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>45813</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>45636</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>45826</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>45831</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>45835</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>45835</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32521,7 +32521,7 @@
         <v>45838</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>45848</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>45848</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>45857</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>45861</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>45859</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>45866</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33042,7 +33042,7 @@
         <v>45877</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33115,7 +33115,7 @@
         <v>45782</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33193,7 +33193,7 @@
         <v>45891</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>45910</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33339,7 +33339,7 @@
         <v>46062</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>

--- a/Översikt ÖVERTORNEÅ.xlsx
+++ b/Översikt ÖVERTORNEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45813</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45403</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45705</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45586</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>45784</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>44635</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>45561</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45833</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45717</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>46273</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>45136</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>45288</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45833</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45586</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45940</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>46216</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45127</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>45096</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>46093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>44880</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>45446</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>45017</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>45985</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>46206</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>45044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>44833</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>45462</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>46272</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>44833</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>44571</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>44791</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>45425</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>46048</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>45846</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>46171</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44587</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>45807</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>45197</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>46269</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>45112</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>44585</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>44504</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44833</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>44494</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>44536</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>44864</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>44536</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>44553</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>44553</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>44571</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>44810</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>44497</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44581</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>44553</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>44557</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>44515</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>44757</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>44538</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>44833</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>44687</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>44557</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>44551</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>44796</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>44692</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>44662</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>44672</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>44585</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44571</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44816</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>45329</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45691</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>45377</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>45227</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>45351</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>45231</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>45772</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>45435</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>45418</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>45481</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>45306</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>45446</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>45467</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>45467</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>45848</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>45573</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>45149</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>46034</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>46034</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>46034</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>46034</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>46034</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>46032</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>45827</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         <v>46034</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>46034</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>45799</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>46038</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>46038</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>46038</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>45889</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>45894</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>46038</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>46038</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45894</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>44589</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>45894</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>45894</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>45632</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>45545</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>45799</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>45602</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>45537</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>46048</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>45137</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>45899</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>44589</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>45622</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>45622</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45673</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45908</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         <v>45910</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>45222</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>45910</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>46056</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45300</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>45559</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>45667</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>46058</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>46057</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>46059</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>46062</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>45011</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>46062</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>46059</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>45516</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45919</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>45351</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>45561</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>44923</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>45926</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>45792</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>45555</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>44910</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>46079</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>46080</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>46080</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>45932</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13326,7 +13326,7 @@
         <v>45139</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>45932</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>45932</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>45586</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>45936</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>46090</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>45938</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>45938</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>45938</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45554</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45940</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>45943</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>46094</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>46094</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45943</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>45142</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>46100</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45460</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>45946</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>45398</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>45217</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>44776</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>45772</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>45351</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>44911</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>45959</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>45961</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>46124</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>45622</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>45965</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>45965</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45965</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>45602</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>44917</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>45965</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>45813</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>45407</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>45636</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>45515</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>45978</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>45979</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>46132</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>45979</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>45979</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>45979</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>45982</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>45985</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45427</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>45960</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45602</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>45727</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>45656</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>45996</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>45995</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>45188</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>44504</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>46003</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>46003</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>46008</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45685</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>46008</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>46008</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>45390</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>46008</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>46010</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>45685</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>46057</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>45376</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>46013</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>45273</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>45686</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>45686</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>46140</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>45826</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>45194</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>46142</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>44529</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>46141</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>46034</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>45526</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45601</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>45831</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>45757</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>45117</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>45547</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>45632</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>45632</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>45632</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>45575</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>44937</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45835</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>46155</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>45838</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>45104</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45835</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>46160</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>46160</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44859</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>46163</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>44484</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>46164</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>46035</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>45670</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>46167</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>46167</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>46167</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45364</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>45848</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>46167</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45743</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>46167</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45848</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>45670</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>46167</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>46167</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>46167</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>44489</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44904</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45857</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45859</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45857</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>46174</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45861</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>44532</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>45504</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>45866</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>44930</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>46177</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>46178</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>45405</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45887</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>46181</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>46178</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45460</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45467</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>46181</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>46178</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45902</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45526</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>44987</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>45595</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23689,7 +23689,7 @@
         <v>46183</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>46185</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23835,7 +23835,7 @@
         <v>46185</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>45685</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>45188</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>45449</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>45589</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>45733</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>45118</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>45509</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>45639</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>46197</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>45953</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>45629</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>45877</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>45453</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>44553</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>45727</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>46251</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>45622</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25159,7 +25159,7 @@
         <v>46251</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25237,7 +25237,7 @@
         <v>45691</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>46210</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>45621</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25456,7 +25456,7 @@
         <v>46162</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>44634</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>45194</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>46206</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>46206</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>45775</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>46136</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>46171</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45870</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>45460</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>46217</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>45516</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44692</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>46184</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>44729</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>46262</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>46265</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>45699</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>44671</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>44672</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26961,7 +26961,7 @@
         <v>44748</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27034,7 +27034,7 @@
         <v>45274</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>46108</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>46267</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27253,7 +27253,7 @@
         <v>46267</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         <v>46269</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
         <v>46272</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27477,7 +27477,7 @@
         <v>44797</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>45451</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>46272</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>46231</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>45395</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27842,7 +27842,7 @@
         <v>45017</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>46276</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27988,7 +27988,7 @@
         <v>45167</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28061,7 +28061,7 @@
         <v>45449</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>46277</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>45136</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28280,7 +28280,7 @@
         <v>45405</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>46274</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>46239</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>44914</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>46182</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28645,7 +28645,7 @@
         <v>46241</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28718,7 +28718,7 @@
         <v>45729</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>45685</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>46283</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28937,7 +28937,7 @@
         <v>46241</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29010,7 +29010,7 @@
         <v>46241</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>44635</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>46094</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
         <v>45576</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>45589</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>44587</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>45574</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>45136</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>45136</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>45281</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29755,7 +29755,7 @@
         <v>45579</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29828,7 +29828,7 @@
         <v>44860</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>46246</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>46167</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30047,7 +30047,7 @@
         <v>46246</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>45390</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>46246</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>45112</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30339,7 +30339,7 @@
         <v>45467</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30412,7 +30412,7 @@
         <v>44601</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
         <v>45092</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30563,7 +30563,7 @@
         <v>44797</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>45136</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>45633</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>45127</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30855,7 +30855,7 @@
         <v>45574</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>45633</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>45700</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>45139</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>45379</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31220,7 +31220,7 @@
         <v>45750</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>45468</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31366,7 +31366,7 @@
         <v>45394</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31439,7 +31439,7 @@
         <v>45707</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         <v>45149</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>45412</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>45377</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31736,7 +31736,7 @@
         <v>45684</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>45039</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>45520</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>45467</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32028,7 +32028,7 @@
         <v>45602</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32101,7 +32101,7 @@
         <v>45369</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32174,7 +32174,7 @@
         <v>45526</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32247,7 +32247,7 @@
         <v>45393</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>45705</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32393,7 +32393,7 @@
         <v>45782</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32471,7 +32471,7 @@
         <v>45891</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32544,7 +32544,7 @@
         <v>45910</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32617,7 +32617,7 @@
         <v>46062</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>

--- a/Översikt ÖVERTORNEÅ.xlsx
+++ b/Översikt ÖVERTORNEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45813</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45403</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45705</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45586</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>45784</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>44635</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>45561</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45833</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45717</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>46273</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>45136</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>45288</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45833</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45586</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45940</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>46216</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45127</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>45096</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>46093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>44880</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>45446</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>45017</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>45985</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>46206</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>45044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>44833</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>45462</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>46272</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>44833</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>44571</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>44791</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>45425</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>46048</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>45846</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>46171</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44587</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>45807</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>45197</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>46269</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>45112</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>44585</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>44504</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44833</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>44494</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>44536</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>44864</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5903,7 +5903,7 @@
         <v>44536</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5976,7 +5976,7 @@
         <v>44553</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         <v>44553</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>44571</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
         <v>44810</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>44497</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44581</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>44553</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>44557</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>44515</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>44757</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>44538</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>44833</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>44687</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>44557</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>44551</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>44796</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>44692</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>44662</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>44672</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>44585</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44571</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44816</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>45329</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45691</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>45377</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>45227</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>45351</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>45231</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>45772</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>45435</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>45418</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>45481</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>45306</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>45446</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>45467</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>45467</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>45848</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>45573</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>45149</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>46034</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>46034</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>46034</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>46034</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>46034</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>46032</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>45827</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         <v>46034</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>46034</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>45799</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>46038</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>46038</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>46038</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>45889</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>45894</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>46038</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>46038</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45894</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>44589</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>45894</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>45894</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>45632</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>45545</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>45799</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>45602</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>45537</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>46048</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>45137</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>45899</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>44589</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>45622</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>45622</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45673</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45908</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         <v>45910</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>45222</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>45910</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>46056</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45300</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>45559</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>45667</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>46058</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>46057</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>46059</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>46062</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
         <v>45011</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>46062</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>46059</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>45516</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12435,7 +12435,7 @@
         <v>45919</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>45351</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12586,7 +12586,7 @@
         <v>45561</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>44923</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>45926</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>45792</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>45555</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>44910</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>46079</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>46080</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>46080</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>45932</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13326,7 +13326,7 @@
         <v>45139</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>45932</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>45932</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>45586</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>45936</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13701,7 +13701,7 @@
         <v>46090</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>45938</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13847,7 +13847,7 @@
         <v>45938</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>45938</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45554</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14071,7 +14071,7 @@
         <v>45940</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>45943</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>46094</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>46094</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45943</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>45142</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>46100</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45460</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>45946</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>45398</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>45217</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>44776</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>45772</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>45351</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>44911</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>45959</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>45961</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15332,7 +15332,7 @@
         <v>46124</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>45622</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>45965</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>45965</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45965</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>45602</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>44917</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>45965</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>45813</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>45407</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>45636</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>45515</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>45978</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>45979</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>46132</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>45979</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>45979</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>45979</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16651,7 +16651,7 @@
         <v>45982</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>45985</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>45427</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16870,7 +16870,7 @@
         <v>45960</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45602</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>45727</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>45656</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>45996</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>45995</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>45188</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>44504</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17454,7 +17454,7 @@
         <v>46003</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>46003</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>46008</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>45685</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17746,7 +17746,7 @@
         <v>46008</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>46008</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>45390</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>46008</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>46010</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>45685</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>46057</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>45376</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>46013</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>45273</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>45686</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>45686</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>46140</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>45826</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>45194</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>46142</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>44529</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>46141</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>46034</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>45526</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45601</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>45831</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>45757</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19430,7 +19430,7 @@
         <v>45117</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19503,7 +19503,7 @@
         <v>45547</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>45632</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19649,7 +19649,7 @@
         <v>45632</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19722,7 +19722,7 @@
         <v>45632</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>45575</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>44937</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45835</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>46155</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>45838</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>45104</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20238,7 +20238,7 @@
         <v>45835</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>46160</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>46160</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>44859</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>46163</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20608,7 +20608,7 @@
         <v>44484</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20681,7 +20681,7 @@
         <v>46164</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>46035</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20827,7 +20827,7 @@
         <v>45670</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>46167</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
         <v>46167</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>46167</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45364</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>45848</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>46167</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21338,7 +21338,7 @@
         <v>45743</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21411,7 +21411,7 @@
         <v>46167</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21484,7 +21484,7 @@
         <v>45848</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21557,7 +21557,7 @@
         <v>45670</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>46167</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21703,7 +21703,7 @@
         <v>46167</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>46167</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>44489</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>44904</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45857</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22068,7 +22068,7 @@
         <v>45859</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45857</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>46174</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22292,7 +22292,7 @@
         <v>45861</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>44532</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>45504</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22516,7 +22516,7 @@
         <v>45866</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>44930</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>46177</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>46178</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>45405</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45887</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>46181</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>46178</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45460</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>45467</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>46181</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>46178</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45902</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45526</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>44987</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>45595</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23689,7 +23689,7 @@
         <v>46183</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>46185</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23835,7 +23835,7 @@
         <v>46185</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>45685</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>45188</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>45449</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>45589</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>45733</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>45118</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>45509</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>45639</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>46197</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>45953</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>45629</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>45877</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>45453</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>44553</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>45727</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>46251</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>45622</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25159,7 +25159,7 @@
         <v>46251</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25237,7 +25237,7 @@
         <v>45691</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>46210</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>45621</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25456,7 +25456,7 @@
         <v>46162</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>44634</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>45194</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>46206</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>46206</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>45775</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>46136</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>46171</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45870</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>45460</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>46217</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>45516</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44692</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>46184</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26523,7 +26523,7 @@
         <v>44729</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>46262</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>46265</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>45699</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>44671</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26888,7 +26888,7 @@
         <v>44672</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26961,7 +26961,7 @@
         <v>44748</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27034,7 +27034,7 @@
         <v>45274</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27107,7 +27107,7 @@
         <v>46108</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>46267</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27253,7 +27253,7 @@
         <v>46267</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         <v>46269</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27404,7 +27404,7 @@
         <v>46272</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27477,7 +27477,7 @@
         <v>44797</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>45451</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>46272</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>46231</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>45395</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27842,7 +27842,7 @@
         <v>45017</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>46276</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27988,7 +27988,7 @@
         <v>45167</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28061,7 +28061,7 @@
         <v>45449</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>46277</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28207,7 +28207,7 @@
         <v>45136</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28280,7 +28280,7 @@
         <v>45405</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28353,7 +28353,7 @@
         <v>46274</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>46239</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         <v>44914</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>46182</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28645,7 +28645,7 @@
         <v>46241</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28718,7 +28718,7 @@
         <v>45729</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>45685</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28864,7 +28864,7 @@
         <v>46283</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28937,7 +28937,7 @@
         <v>46241</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29010,7 +29010,7 @@
         <v>46241</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>44635</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>46094</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
         <v>45576</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>45589</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>44587</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>45574</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>45136</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>45136</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>45281</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29755,7 +29755,7 @@
         <v>45579</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29828,7 +29828,7 @@
         <v>44860</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>46246</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29974,7 +29974,7 @@
         <v>46167</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30047,7 +30047,7 @@
         <v>46246</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>45390</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>46246</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>45112</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30339,7 +30339,7 @@
         <v>45467</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30412,7 +30412,7 @@
         <v>44601</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
         <v>45092</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30563,7 +30563,7 @@
         <v>44797</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30636,7 +30636,7 @@
         <v>45136</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30709,7 +30709,7 @@
         <v>45633</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30782,7 +30782,7 @@
         <v>45127</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30855,7 +30855,7 @@
         <v>45574</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>45633</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>45700</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>45139</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>45379</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31220,7 +31220,7 @@
         <v>45750</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>45468</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31366,7 +31366,7 @@
         <v>45394</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31439,7 +31439,7 @@
         <v>45707</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         <v>45149</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>45412</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>45377</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31736,7 +31736,7 @@
         <v>45684</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>45039</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         <v>45520</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31955,7 +31955,7 @@
         <v>45467</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32028,7 +32028,7 @@
         <v>45602</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32101,7 +32101,7 @@
         <v>45369</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32174,7 +32174,7 @@
         <v>45526</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32247,7 +32247,7 @@
         <v>45393</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32320,7 +32320,7 @@
         <v>45705</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32393,7 +32393,7 @@
         <v>45782</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32471,7 +32471,7 @@
         <v>45891</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32544,7 +32544,7 @@
         <v>45910</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32617,7 +32617,7 @@
         <v>46062</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>

--- a/Översikt ÖVERTORNEÅ.xlsx
+++ b/Översikt ÖVERTORNEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45813</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45403</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45705</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45586</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>45784</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>44635</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>45561</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45717</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>45833</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>46273</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>45136</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>45288</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45833</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45586</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45940</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>45127</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>46216</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>45096</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>46093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>44880</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>45446</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>45017</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>45985</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>46206</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>45044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>44833</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>45462</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>46272</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>44833</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>44571</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>46048</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>44587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>45846</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>44791</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>46171</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45807</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>46269</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>45112</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>45425</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>44585</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>44504</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>44833</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>44494</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>44536</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44864</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>44536</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>44553</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>44553</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>44571</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>44810</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44497</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>44581</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>44557</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>44553</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>44515</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>44757</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>44538</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>44833</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>44687</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>44557</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>44551</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>44796</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>44692</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>44662</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>44672</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>44585</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>44571</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>44816</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>45673</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45227</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>44797</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>44692</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45231</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>45136</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45576</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>45468</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>45554</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>45622</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>45622</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>45377</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>44987</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>45142</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>44504</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>45453</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>45602</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>45526</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>45602</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>45393</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>46003</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>45516</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>45149</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>46003</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>45545</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>46008</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>46008</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>45573</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>46008</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>46008</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>45656</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>46010</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45136</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>45691</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>45827</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>45889</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>44910</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>45848</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>45894</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>45894</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>45894</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>45894</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>44589</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>46034</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>45899</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>46034</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>46034</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>46034</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>46034</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>46032</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>46034</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>46034</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>44489</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>44671</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>45194</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>46038</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         <v>45908</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>46038</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>46038</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>46038</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         <v>46038</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>45910</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>45910</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>46048</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>45137</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>45222</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>45799</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         <v>45799</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>45274</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>45602</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         <v>45919</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>45460</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12769,7 +12769,7 @@
         <v>45395</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>45667</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>46056</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         <v>46057</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>45926</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
         <v>46058</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>46059</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>45686</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>45699</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>46059</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>46062</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>46062</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>45932</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>45932</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>45932</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13884,7 +13884,7 @@
         <v>45936</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>45938</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>45139</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>44748</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>45938</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>45938</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>45943</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>45940</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>45394</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>45943</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>45946</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>46079</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>46080</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>46080</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>45792</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>45813</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>45959</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>45750</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>46090</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>45961</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>45965</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>45965</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>45965</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>45965</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>46094</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>45633</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>46094</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>46100</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>44553</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>45632</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>44904</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>45978</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>45979</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>45979</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45979</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>45979</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>44911</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>45691</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>45555</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>45636</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>45460</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>45985</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>45982</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>45407</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>45390</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>45467</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>45960</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>46124</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>45995</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>45996</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>44860</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>45826</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>45831</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45127</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>46132</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>45835</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45835</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>45589</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>45537</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>45838</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45633</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>45194</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>45684</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>45547</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45622</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>45621</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>45727</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>45848</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>45848</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>45729</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19039,7 +19039,7 @@
         <v>44914</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45504</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>45575</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>45857</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>45601</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>45861</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>45733</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>45859</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>46140</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>45398</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>46141</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>45866</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>44729</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45574</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45405</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>44917</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>44587</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>46013</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>45451</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>46057</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>46034</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>45376</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>46142</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>45526</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>45306</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>45351</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45118</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>44930</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>45217</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>46155</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45772</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>45412</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>45167</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45039</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>46160</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21624,7 +21624,7 @@
         <v>46160</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>46163</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>46164</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>46167</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>45743</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>46167</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>45877</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>46167</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>46167</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>46035</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>46167</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22427,7 +22427,7 @@
         <v>46167</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>46167</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>45559</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>46167</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>45857</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>45670</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         <v>45435</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22943,7 +22943,7 @@
         <v>45670</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>46174</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23089,7 +23089,7 @@
         <v>44529</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23162,7 +23162,7 @@
         <v>46178</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23235,7 +23235,7 @@
         <v>46178</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23308,7 +23308,7 @@
         <v>45427</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23381,7 +23381,7 @@
         <v>46177</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>46178</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>45273</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>46181</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>45887</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23746,7 +23746,7 @@
         <v>46183</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>46181</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23892,7 +23892,7 @@
         <v>45405</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>45902</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>46185</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>46185</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>45589</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24262,7 +24262,7 @@
         <v>45632</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>45632</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>45953</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         <v>45281</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>46197</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>45390</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45700</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>45460</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24851,7 +24851,7 @@
         <v>46162</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>46210</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>44776</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45686</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>44589</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>46206</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>45870</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>45685</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>46206</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>45775</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>46217</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45467</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>46171</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>46136</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25908,7 +25908,7 @@
         <v>46184</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>45622</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>45351</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>45467</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>46262</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>46265</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44859</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>45104</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26492,7 +26492,7 @@
         <v>46108</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>45092</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>46267</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>45685</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>46267</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>46269</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>45639</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>45139</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>46272</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>46231</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>46272</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>46276</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>46277</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27451,7 +27451,7 @@
         <v>46274</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27524,7 +27524,7 @@
         <v>45446</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>45509</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>45449</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>45377</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>45188</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>45188</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>45351</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>46241</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>46239</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>44601</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>46283</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45757</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>44635</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>46241</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>46094</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28619,7 +28619,7 @@
         <v>45574</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28692,7 +28692,7 @@
         <v>46241</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28765,7 +28765,7 @@
         <v>45136</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28838,7 +28838,7 @@
         <v>45136</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28911,7 +28911,7 @@
         <v>46182</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28984,7 +28984,7 @@
         <v>45586</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29057,7 +29057,7 @@
         <v>45579</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>46246</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>46246</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         <v>46246</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>45329</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29422,7 +29422,7 @@
         <v>45526</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29495,7 +29495,7 @@
         <v>46293</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>45364</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>46167</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>45149</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29792,7 +29792,7 @@
         <v>44923</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29865,7 +29865,7 @@
         <v>45772</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>45449</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30011,7 +30011,7 @@
         <v>45632</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30084,7 +30084,7 @@
         <v>46251</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>45011</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30235,7 +30235,7 @@
         <v>46251</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30313,7 +30313,7 @@
         <v>45467</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>45112</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30459,7 +30459,7 @@
         <v>45602</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30532,7 +30532,7 @@
         <v>45481</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30605,7 +30605,7 @@
         <v>44532</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30678,7 +30678,7 @@
         <v>45685</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30751,7 +30751,7 @@
         <v>45561</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
         <v>45117</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30897,7 +30897,7 @@
         <v>45516</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30970,7 +30970,7 @@
         <v>45595</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         <v>44797</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>45017</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>45685</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>44634</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         <v>44937</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>45515</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>45418</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>45707</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>45727</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>45379</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31773,7 +31773,7 @@
         <v>44672</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31846,7 +31846,7 @@
         <v>44484</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31919,7 +31919,7 @@
         <v>45300</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31992,7 +31992,7 @@
         <v>45629</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32065,7 +32065,7 @@
         <v>45520</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>45467</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>45369</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>45705</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>45782</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>45891</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>45910</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>46062</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>

--- a/Översikt ÖVERTORNEÅ.xlsx
+++ b/Översikt ÖVERTORNEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45813</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45403</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45705</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45586</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>45784</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>44635</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>45561</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45717</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>45833</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>46273</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>45136</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>45288</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45833</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45586</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45940</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>45127</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>46216</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>45096</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>46093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>44880</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
         <v>45446</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>45017</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         <v>45985</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>46206</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>45044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>44833</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>45462</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>46272</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>44833</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>44571</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         <v>46048</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>44587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>45846</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>44791</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>46171</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45807</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>46269</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>45112</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>45425</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>44585</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>44504</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
         <v>44833</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>44494</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>44536</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44864</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>44536</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>44553</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>44553</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>44571</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>44810</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6159,7 +6159,7 @@
         <v>44497</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>44581</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>44557</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>44553</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>44515</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>44757</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>44538</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>44833</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>44687</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>44557</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>44551</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>44796</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>44692</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>44662</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>44672</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>44585</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>44571</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>44816</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>45673</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>45227</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>44797</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>44692</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45231</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>45136</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45576</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         <v>45468</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>45554</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>45622</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         <v>45622</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>45377</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8364,7 +8364,7 @@
         <v>44987</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8437,7 +8437,7 @@
         <v>45142</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>44504</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>45453</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>45602</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>45526</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>45602</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>45393</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>46003</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>45516</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>45149</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>46003</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>45545</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>46008</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>46008</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>45573</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9537,7 +9537,7 @@
         <v>46008</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9610,7 +9610,7 @@
         <v>46008</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>45656</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>46010</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45136</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>45691</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>45827</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>45889</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>44910</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>45848</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>45894</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>45894</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>45894</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10491,7 +10491,7 @@
         <v>45894</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>44589</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>46034</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10715,7 +10715,7 @@
         <v>45899</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>46034</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>46034</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>46034</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>46034</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v>46032</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11158,7 +11158,7 @@
         <v>46034</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>46034</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>44489</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>44671</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>45194</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>46038</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         <v>45908</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>46038</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>46038</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>46038</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         <v>46038</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>45910</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12034,7 +12034,7 @@
         <v>45910</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>46048</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>45137</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         <v>45222</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12326,7 +12326,7 @@
         <v>45799</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12399,7 +12399,7 @@
         <v>45799</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12472,7 +12472,7 @@
         <v>45274</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12545,7 +12545,7 @@
         <v>45602</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         <v>45919</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>45460</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12769,7 +12769,7 @@
         <v>45395</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
         <v>45667</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>46056</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         <v>46057</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>45926</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13139,7 +13139,7 @@
         <v>46058</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13212,7 +13212,7 @@
         <v>46059</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>45686</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>45699</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>46059</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>46062</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>46062</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>45932</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>45932</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>45932</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13884,7 +13884,7 @@
         <v>45936</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>45938</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>45139</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>44748</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14181,7 +14181,7 @@
         <v>45938</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14254,7 +14254,7 @@
         <v>45938</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>45943</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>45940</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>45394</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>45943</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>45946</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>46079</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>46080</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>46080</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14916,7 +14916,7 @@
         <v>45792</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14989,7 +14989,7 @@
         <v>45813</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>45959</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15140,7 +15140,7 @@
         <v>45750</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>46090</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>45961</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>45965</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>45965</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>45965</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15583,7 +15583,7 @@
         <v>45965</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>46094</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15729,7 +15729,7 @@
         <v>45633</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>46094</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>46100</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>44553</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>45632</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
         <v>44904</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16167,7 +16167,7 @@
         <v>45978</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>45979</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>45979</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45979</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         <v>45979</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16532,7 +16532,7 @@
         <v>44911</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>45691</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>45555</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>45636</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>45460</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>45985</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>45982</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>45407</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>45390</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>45467</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>45960</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17340,7 +17340,7 @@
         <v>46124</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>45995</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>45996</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17559,7 +17559,7 @@
         <v>44860</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>45826</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>45831</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>45127</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>46132</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>45835</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45835</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>45589</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>45537</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>45838</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45633</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>45194</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>45684</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
         <v>45547</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18601,7 +18601,7 @@
         <v>45622</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>45621</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>45727</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>45848</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>45848</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>45729</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19039,7 +19039,7 @@
         <v>44914</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45504</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19190,7 +19190,7 @@
         <v>45575</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19263,7 +19263,7 @@
         <v>45857</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>45601</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>45861</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>45733</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>45859</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>46140</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>45398</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>46141</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19857,7 +19857,7 @@
         <v>45866</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>44729</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45574</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45405</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>44917</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>44587</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>46013</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>45451</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>46057</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>46034</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>45376</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>46142</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>45526</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>45306</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>45351</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45118</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>44930</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>45217</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>46155</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45772</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>45412</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>45167</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45039</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>46160</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21624,7 +21624,7 @@
         <v>46160</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>46163</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>46164</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>46167</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>45743</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>46167</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>45877</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>46167</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>46167</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>46035</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>46167</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22427,7 +22427,7 @@
         <v>46167</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>46167</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22573,7 +22573,7 @@
         <v>45559</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>46167</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>45857</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>45670</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         <v>45435</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22943,7 +22943,7 @@
         <v>45670</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>46174</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23089,7 +23089,7 @@
         <v>44529</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23162,7 +23162,7 @@
         <v>46178</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23235,7 +23235,7 @@
         <v>46178</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23308,7 +23308,7 @@
         <v>45427</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23381,7 +23381,7 @@
         <v>46177</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>46178</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23527,7 +23527,7 @@
         <v>45273</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>46181</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23673,7 +23673,7 @@
         <v>45887</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23746,7 +23746,7 @@
         <v>46183</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>46181</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23892,7 +23892,7 @@
         <v>45405</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>45902</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>46185</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>46185</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>45589</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24262,7 +24262,7 @@
         <v>45632</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>45632</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>45953</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         <v>45281</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>46197</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>45390</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45700</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>45460</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24851,7 +24851,7 @@
         <v>46162</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>46210</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>44776</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45686</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>44589</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>46206</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>45870</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25377,7 +25377,7 @@
         <v>45685</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25450,7 +25450,7 @@
         <v>46206</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>45775</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25606,7 +25606,7 @@
         <v>46217</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45467</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>46171</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>46136</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25908,7 +25908,7 @@
         <v>46184</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>45622</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>45351</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>45467</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>46262</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>46265</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44859</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>45104</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26492,7 +26492,7 @@
         <v>46108</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>45092</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>46267</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>45685</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>46267</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>46269</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26940,7 +26940,7 @@
         <v>45639</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>45139</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>46272</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>46231</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>46272</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>46276</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>46277</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27451,7 +27451,7 @@
         <v>46274</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27524,7 +27524,7 @@
         <v>45446</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>45509</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27670,7 +27670,7 @@
         <v>45449</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>45377</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>45188</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27889,7 +27889,7 @@
         <v>45188</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>45351</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>46241</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>46239</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>44601</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28254,7 +28254,7 @@
         <v>46283</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         <v>45757</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28400,7 +28400,7 @@
         <v>44635</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28473,7 +28473,7 @@
         <v>46241</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28546,7 +28546,7 @@
         <v>46094</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28619,7 +28619,7 @@
         <v>45574</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28692,7 +28692,7 @@
         <v>46241</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28765,7 +28765,7 @@
         <v>45136</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28838,7 +28838,7 @@
         <v>45136</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28911,7 +28911,7 @@
         <v>46182</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28984,7 +28984,7 @@
         <v>45586</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29057,7 +29057,7 @@
         <v>45579</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>46246</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>46246</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         <v>46246</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>45329</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29422,7 +29422,7 @@
         <v>45526</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29495,7 +29495,7 @@
         <v>46293</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29573,7 +29573,7 @@
         <v>45364</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>46167</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>45149</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29792,7 +29792,7 @@
         <v>44923</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29865,7 +29865,7 @@
         <v>45772</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29938,7 +29938,7 @@
         <v>45449</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30011,7 +30011,7 @@
         <v>45632</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30084,7 +30084,7 @@
         <v>46251</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>45011</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30235,7 +30235,7 @@
         <v>46251</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30313,7 +30313,7 @@
         <v>45467</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         <v>45112</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30459,7 +30459,7 @@
         <v>45602</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30532,7 +30532,7 @@
         <v>45481</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30605,7 +30605,7 @@
         <v>44532</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30678,7 +30678,7 @@
         <v>45685</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30751,7 +30751,7 @@
         <v>45561</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
         <v>45117</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30897,7 +30897,7 @@
         <v>45516</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30970,7 +30970,7 @@
         <v>45595</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         <v>44797</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>45017</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>45685</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>44634</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         <v>44937</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>45515</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>45418</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>45707</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>45727</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31700,7 +31700,7 @@
         <v>45379</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31773,7 +31773,7 @@
         <v>44672</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31846,7 +31846,7 @@
         <v>44484</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31919,7 +31919,7 @@
         <v>45300</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31992,7 +31992,7 @@
         <v>45629</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32065,7 +32065,7 @@
         <v>45520</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>45467</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>45369</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>45705</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>45782</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>45891</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>45910</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>46062</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>

--- a/Översikt ÖVERTORNEÅ.xlsx
+++ b/Översikt ÖVERTORNEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45813</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45403</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45705</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45586</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>45784</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>44635</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>45561</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45833</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45717</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>46273</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>45136</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>45288</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45833</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45127</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>45096</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>45940</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>46216</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>44880</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>46093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45446</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45017</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>45044</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>45985</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>46206</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>46300</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>44833</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>45462</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>46272</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>46301</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>44833</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>44571</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>44791</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>45425</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>44587</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45846</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>45112</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>46048</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>46171</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>45807</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>46269</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>44585</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>44504</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>44833</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>44494</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>44536</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>44864</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>44536</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>44553</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>44553</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44571</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>44796</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>44692</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>44757</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>44672</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>44538</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>44497</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>44833</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>44662</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>44585</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44687</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>44581</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44553</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44557</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44557</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44571</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>45351</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>45231</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>44816</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>44551</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>45772</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>45136</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>45757</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>45117</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>45547</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45632</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>45632</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45632</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45633</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45127</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>45575</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>45574</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>45435</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>44937</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>45377</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>45104</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>45329</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>45691</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>45227</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>45633</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>45700</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>44859</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>45139</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>44484</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>45418</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>45364</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>45379</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>45750</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>45481</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>44489</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>45446</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>45306</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>45467</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>45467</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>45468</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>45149</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>44904</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>45827</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>45573</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>44532</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>45394</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>45707</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>45149</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>45504</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>44930</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>45889</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>45894</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>45894</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>45894</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>45894</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>45412</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>45377</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>45899</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>44589</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>45684</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>45039</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>44589</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>45632</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>45545</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>45908</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>45537</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>45460</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>45910</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>45910</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>45467</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>45520</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>45467</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>45526</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>45622</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>45622</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>45673</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>44987</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>45595</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>45685</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45188</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45300</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>45559</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>45602</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>45449</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>45589</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>45011</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>45919</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>45516</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>45369</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>45351</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>45526</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>45561</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>45393</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>45705</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45733</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>45118</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>45926</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>45509</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>44923</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>45639</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>45555</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>44910</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>45629</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>45586</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>45453</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>45932</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>44553</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>45932</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>45932</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>45727</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>45799</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>45799</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>45602</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45137</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>45936</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>45554</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45222</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>45142</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>45622</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>45938</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>45460</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>45398</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>45217</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>45139</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>45691</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>44776</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>45938</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>45938</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>45940</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>45943</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>45943</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>45946</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>45621</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>45813</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>45772</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>45636</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>45351</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>44634</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45194</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>44911</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>45622</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>45826</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>45602</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>44917</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>45460</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45516</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>45831</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>45407</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>45959</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>45515</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>45835</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45838</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>44692</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>45835</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>45961</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>45965</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>45965</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>45965</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>44729</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>45699</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>44671</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>44672</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>45965</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>45427</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44748</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45274</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45602</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45727</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45848</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>45848</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45656</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>45859</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45857</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>45861</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>45978</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>45866</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>45979</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>45188</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>44504</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>44797</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>45451</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45685</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>45390</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45979</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>45979</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>45685</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>45979</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45982</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45395</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>45877</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45273</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45017</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>46094</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>46094</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45686</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45686</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>45167</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>45985</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>45449</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>45136</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>45405</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>46100</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>45194</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>44529</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>44914</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>45960</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45526</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>45729</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>45601</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>45685</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>46124</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>45996</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45995</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>45576</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>46132</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45589</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>46003</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>44587</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>45574</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23497,7 +23497,7 @@
         <v>46003</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>46008</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>45281</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>45579</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>46008</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>46008</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>44860</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>46008</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>46010</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>45390</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45848</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>45112</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>45467</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>44601</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>46034</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>46034</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>46034</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>46034</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>46034</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>46032</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>46034</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>46034</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>45092</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>46038</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>46038</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>46038</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>46038</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>46038</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>46057</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>45376</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>46013</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25765,7 +25765,7 @@
         <v>44797</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25838,7 +25838,7 @@
         <v>46048</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>46140</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>46142</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>46056</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>45667</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>46058</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>46057</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>46059</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>46141</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>46034</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>46062</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>46062</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>46059</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>45792</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>46079</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>46080</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>46080</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>46155</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>46160</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>46160</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>46090</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         <v>46163</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>46164</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>46035</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>45670</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>46167</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>46167</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27809,7 +27809,7 @@
         <v>46167</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27882,7 +27882,7 @@
         <v>46167</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>45743</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>46167</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>45670</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28174,7 +28174,7 @@
         <v>46167</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>46167</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>46167</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28393,7 +28393,7 @@
         <v>45857</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>46174</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28539,7 +28539,7 @@
         <v>46177</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>46178</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>45405</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>45887</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>46181</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28904,7 +28904,7 @@
         <v>46178</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
         <v>46181</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>46178</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29123,7 +29123,7 @@
         <v>45902</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         <v>46183</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>46185</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>46185</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>46197</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>45953</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29561,7 +29561,7 @@
         <v>46210</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>46162</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29712,7 +29712,7 @@
         <v>46206</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29790,7 +29790,7 @@
         <v>46206</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29868,7 +29868,7 @@
         <v>45775</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>46136</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>46171</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>45870</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>46217</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>46184</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>46265</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>46108</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>46267</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>46267</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>46269</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>46272</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>46272</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30842,7 +30842,7 @@
         <v>46231</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>46276</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>46277</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>46274</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31134,7 +31134,7 @@
         <v>46239</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31207,7 +31207,7 @@
         <v>46182</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31280,7 +31280,7 @@
         <v>46241</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>46283</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31426,7 +31426,7 @@
         <v>46241</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31499,7 +31499,7 @@
         <v>46241</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>44635</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>46094</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31718,7 +31718,7 @@
         <v>45136</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31791,7 +31791,7 @@
         <v>45136</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31864,7 +31864,7 @@
         <v>46246</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31937,7 +31937,7 @@
         <v>46167</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>46246</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32083,7 +32083,7 @@
         <v>46246</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32156,7 +32156,7 @@
         <v>46293</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>46251</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>46251</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>46302</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>46301</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>46301</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>46301</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>46301</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32755,7 +32755,7 @@
         <v>46301</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32828,7 +32828,7 @@
         <v>46304</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>46262</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>45782</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>45891</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33125,7 +33125,7 @@
         <v>45910</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>46062</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>

--- a/Översikt ÖVERTORNEÅ.xlsx
+++ b/Översikt ÖVERTORNEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45813</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45403</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45705</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45586</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>45784</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>44635</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>45561</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45833</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         <v>45717</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>46273</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>45136</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>45288</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45833</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45127</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>45096</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>45940</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>46216</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>44880</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>46093</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45446</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45017</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>45044</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>45985</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>46206</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>46300</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>44833</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>45462</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>46272</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>46301</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>44833</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>44571</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>44791</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>45425</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>44587</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>45846</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>45112</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>46048</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>46171</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>45807</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>46269</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>44585</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>44504</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>44833</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>44494</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>44536</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>44864</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>44536</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>44553</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>44553</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44571</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>44796</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>44692</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>44515</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>44757</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         <v>44672</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>44810</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>44538</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>44497</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>44833</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>44662</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>44585</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44687</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>44581</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44553</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44557</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44557</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44571</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>45351</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>45231</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>44816</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>44551</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>45772</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         <v>45136</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>45757</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>45117</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>45547</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45632</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>45632</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45632</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45633</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45127</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>45575</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>45574</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>45435</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>44937</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>45377</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>45104</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8903,7 +8903,7 @@
         <v>45329</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>45691</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>45227</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>45633</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         <v>45700</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>44859</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>45139</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>44484</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>45418</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>45364</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9633,7 +9633,7 @@
         <v>45379</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>45750</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
         <v>45481</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>44489</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>45446</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>45306</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>45467</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>45467</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>45468</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>45149</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>44904</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>45827</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>45573</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>44532</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>45394</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>45707</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>45149</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>45504</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>44930</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>45889</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>45894</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>45894</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
         <v>45894</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>45894</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>45412</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11478,7 +11478,7 @@
         <v>45377</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11551,7 +11551,7 @@
         <v>45899</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>44589</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>45684</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>45039</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>44589</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>45632</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>45545</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>45908</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>45537</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>45460</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>45910</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>45910</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>45467</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>45520</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>45467</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>45526</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>45622</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>45622</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>45673</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>44987</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>45595</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>45685</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45188</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45300</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>45559</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>45602</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>45449</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>45589</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>45011</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>45919</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>45516</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         <v>45369</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13907,7 +13907,7 @@
         <v>45351</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>45526</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>45561</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>45393</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>45705</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45733</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>45118</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>45926</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>45509</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>44923</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>45639</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>45555</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>44910</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>45629</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>45586</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15007,7 +15007,7 @@
         <v>45453</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         <v>45932</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>44553</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>45932</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>45932</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>45727</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>45799</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>45799</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>45602</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45137</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>45936</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>45554</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45222</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>45142</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>45622</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>45938</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>45460</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>45398</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>45217</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>45139</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>45691</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>44776</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>45938</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>45938</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>45940</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>45943</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>45943</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>45946</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>45621</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>45813</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>45772</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>45636</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17383,7 +17383,7 @@
         <v>45351</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>44634</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45194</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>44911</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>45622</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>45826</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>45602</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>44917</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>45460</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45516</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>45831</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>45407</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>45959</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>45515</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>45835</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45838</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>44692</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>45835</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>45961</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>45965</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>45965</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18946,7 +18946,7 @@
         <v>45965</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19019,7 +19019,7 @@
         <v>44729</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19092,7 +19092,7 @@
         <v>45699</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>44671</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>44672</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19311,7 +19311,7 @@
         <v>45965</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>45427</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44748</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45274</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45602</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45727</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45848</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>45848</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45656</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19968,7 +19968,7 @@
         <v>45859</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45857</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>45861</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>45978</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>45866</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>45979</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>45188</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>44504</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>44797</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>45451</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45685</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>45390</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45979</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>45979</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>45685</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>45979</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>45982</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45395</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>45877</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45273</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45017</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>46094</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21584,7 +21584,7 @@
         <v>46094</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21657,7 +21657,7 @@
         <v>45686</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21730,7 +21730,7 @@
         <v>45686</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>45167</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21876,7 +21876,7 @@
         <v>45985</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>45449</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22022,7 +22022,7 @@
         <v>45136</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22095,7 +22095,7 @@
         <v>45405</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>46100</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>45194</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>44529</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22387,7 +22387,7 @@
         <v>44914</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>45960</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45526</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>45729</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>45601</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>45685</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>46124</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>45996</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45995</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>45576</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>46132</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>45589</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>46003</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>44587</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>45574</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23497,7 +23497,7 @@
         <v>46003</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23570,7 +23570,7 @@
         <v>46008</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>45281</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23716,7 +23716,7 @@
         <v>45579</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>46008</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>46008</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>44860</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>46008</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>46010</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>45390</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>45848</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>45112</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>45467</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>44601</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>46034</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>46034</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>46034</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>46034</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24811,7 +24811,7 @@
         <v>46034</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>46032</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>46034</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>46034</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>45092</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>46038</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>46038</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>46038</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>46038</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>46038</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>46057</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25619,7 +25619,7 @@
         <v>45376</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>46013</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25765,7 +25765,7 @@
         <v>44797</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25838,7 +25838,7 @@
         <v>46048</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>46140</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25984,7 +25984,7 @@
         <v>46142</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26057,7 +26057,7 @@
         <v>46056</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26130,7 +26130,7 @@
         <v>45667</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26203,7 +26203,7 @@
         <v>46058</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26276,7 +26276,7 @@
         <v>46057</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>46059</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26422,7 +26422,7 @@
         <v>46141</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>46034</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>46062</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>46062</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>46059</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26787,7 +26787,7 @@
         <v>45792</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>46079</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26933,7 +26933,7 @@
         <v>46080</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>46080</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>46155</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>46160</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>46160</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>46090</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         <v>46163</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>46164</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>46035</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27590,7 +27590,7 @@
         <v>45670</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>46167</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>46167</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27809,7 +27809,7 @@
         <v>46167</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27882,7 +27882,7 @@
         <v>46167</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27955,7 +27955,7 @@
         <v>45743</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>46167</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>45670</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28174,7 +28174,7 @@
         <v>46167</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>46167</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>46167</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28393,7 +28393,7 @@
         <v>45857</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>46174</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28539,7 +28539,7 @@
         <v>46177</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>46178</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>45405</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>45887</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>46181</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28904,7 +28904,7 @@
         <v>46178</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
         <v>46181</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>46178</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29123,7 +29123,7 @@
         <v>45902</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         <v>46183</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>46185</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>46185</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>46197</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>45953</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29561,7 +29561,7 @@
         <v>46210</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>46162</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29712,7 +29712,7 @@
         <v>46206</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29790,7 +29790,7 @@
         <v>46206</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29868,7 +29868,7 @@
         <v>45775</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>46136</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>46171</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>45870</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>46217</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>46184</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>46265</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>46108</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>46267</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>46267</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>46269</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30696,7 +30696,7 @@
         <v>46272</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>46272</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30842,7 +30842,7 @@
         <v>46231</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>46276</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>46277</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>46274</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31134,7 +31134,7 @@
         <v>46239</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31207,7 +31207,7 @@
         <v>46182</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31280,7 +31280,7 @@
         <v>46241</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>46283</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31426,7 +31426,7 @@
         <v>46241</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31499,7 +31499,7 @@
         <v>46241</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>44635</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31645,7 +31645,7 @@
         <v>46094</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31718,7 +31718,7 @@
         <v>45136</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31791,7 +31791,7 @@
         <v>45136</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31864,7 +31864,7 @@
         <v>46246</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31937,7 +31937,7 @@
         <v>46167</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>46246</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32083,7 +32083,7 @@
         <v>46246</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32156,7 +32156,7 @@
         <v>46293</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>46251</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>46251</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32390,7 +32390,7 @@
         <v>46302</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>46301</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>46301</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>46301</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32682,7 +32682,7 @@
         <v>46301</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32755,7 +32755,7 @@
         <v>46301</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32828,7 +32828,7 @@
         <v>46304</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>46262</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>45782</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>45891</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33125,7 +33125,7 @@
         <v>45910</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33198,7 +33198,7 @@
         <v>46062</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>

--- a/Översikt ÖVERTORNEÅ.xlsx
+++ b/Översikt ÖVERTORNEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45813</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45403</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45705</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45586</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>45784</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>44635</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>45561</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45717</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>46273</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45136</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>45288</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>45833</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45833</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45127</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>45940</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>46216</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45096</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>46093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>44880</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45446</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45017</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>45985</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>46206</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>46300</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>45044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>44833</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>45462</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>46272</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>46301</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>44833</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>44571</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>44587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44791</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>46048</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>46171</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>45807</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>45112</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>45425</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>46269</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>45846</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>44585</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>44504</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>44833</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>44494</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>44536</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>44864</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>44536</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>44553</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>44553</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44571</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>44810</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>44497</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>44581</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44553</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>44557</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>44515</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>44757</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>44538</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>44833</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>44687</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>44557</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44551</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>44796</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44692</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44662</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44672</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44585</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>44571</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>44816</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>45673</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>45231</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>44692</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>45136</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>45576</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>45227</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44797</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>45468</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>45554</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>45622</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>45622</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>45377</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>44504</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>44987</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>45142</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         <v>45453</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>45602</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>45516</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>45545</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>45573</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>45656</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>45691</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>45136</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
         <v>44910</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>44671</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>45194</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>44489</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>45274</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>45460</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>45699</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>45395</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>45686</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>44748</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>45394</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>45750</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>45633</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>44553</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>45632</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>44904</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>45555</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>44911</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>45691</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>45460</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>45407</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>45390</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>45827</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>45889</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>44860</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>45894</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>45894</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>45127</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>45894</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>45894</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>44589</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>45149</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>46140</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>45899</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>46141</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>46013</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>46057</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>46034</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>45376</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>45908</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>45589</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>45910</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>45537</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>46142</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>45910</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>45633</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>45194</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>45684</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>45919</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>45547</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>45622</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>45621</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>45727</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>45729</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>44914</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>45504</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>45926</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>45932</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>45932</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>45932</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>45575</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>45936</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>45938</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>45938</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>45938</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         <v>45943</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         <v>45940</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>45601</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>45943</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>45733</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>45946</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>46155</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>45398</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>44729</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>45574</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>45405</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>45959</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>44917</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>44587</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>45451</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45961</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>45965</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15344,7 +15344,7 @@
         <v>45965</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>45965</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>45965</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>45526</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>46160</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>46160</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>45306</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>46163</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
         <v>45978</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>45979</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>45979</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>45979</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>45979</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>45351</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>45118</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>46164</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>46167</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>45743</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>46167</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45985</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45982</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>46167</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>44930</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>46167</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>46035</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>45217</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>46167</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>46167</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>46167</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>45772</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>46167</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45412</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>45857</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>45670</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>45167</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>45960</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>45670</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>45039</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>45995</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>45996</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>45559</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>46003</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>45435</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>46003</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>46008</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>46008</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>46008</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>46008</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>46174</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>46010</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>44529</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>45427</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>45273</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>45848</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>46034</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>46034</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>46034</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>46034</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>46034</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>46032</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>46034</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>46034</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>46178</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>46178</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>46038</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>46038</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>46038</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>46038</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>46038</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>46177</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>46178</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>45589</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>46048</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45632</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45632</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>46181</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>45887</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>46183</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>46181</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45405</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>45902</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>45667</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>46056</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>46057</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>46058</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>46059</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>45281</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>46059</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>46062</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>46062</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         <v>45390</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45700</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>46185</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>45460</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         <v>46079</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>46185</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>46080</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>46080</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>45792</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>44776</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22664,7 +22664,7 @@
         <v>46090</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>46094</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>45686</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>46094</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         <v>44589</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>45685</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>46100</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>45622</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>45351</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>45953</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>44859</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>45104</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>46197</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>45092</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>45685</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>46124</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>45639</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>45139</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>46132</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>45446</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>45509</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>45449</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45377</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>45188</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>45188</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>45351</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>46162</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>46210</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>44601</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>45757</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>46206</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45870</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>46206</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>45775</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         <v>46217</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>45574</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>46171</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>46136</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>45586</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>45579</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>46108</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25697,7 +25697,7 @@
         <v>45329</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>45526</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>46272</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>46231</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>45364</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26062,7 +26062,7 @@
         <v>46272</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>45149</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>46276</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>46277</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>44923</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>46274</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>45772</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>45449</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>45632</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>45011</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45112</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>46241</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>46239</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>45602</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>45481</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>46283</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>44532</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>44635</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>46241</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>46094</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>45685</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45561</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>46241</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45136</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>45136</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>46182</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>46246</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>46246</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>46246</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>45117</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>45516</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>45595</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>46293</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>44797</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>46167</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45017</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45685</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44634</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44937</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>45515</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>45418</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>45707</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>45727</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>45379</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29279,7 +29279,7 @@
         <v>44672</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>46251</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29430,7 +29430,7 @@
         <v>46251</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>45300</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29581,7 +29581,7 @@
         <v>46301</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>46301</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45629</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45520</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>46301</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>46301</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>45705</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>45602</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>45526</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30238,7 +30238,7 @@
         <v>46301</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>45393</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>46302</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>46304</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>45137</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30603,7 +30603,7 @@
         <v>45222</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>45799</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>45799</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>46262</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30895,7 +30895,7 @@
         <v>45602</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>46265</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31041,7 +31041,7 @@
         <v>46184</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>45139</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>45813</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31265,7 +31265,7 @@
         <v>46269</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>45636</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>46311</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>46311</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31562,7 +31562,7 @@
         <v>46267</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31635,7 +31635,7 @@
         <v>46267</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>45826</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31781,7 +31781,7 @@
         <v>45831</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>45835</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31937,7 +31937,7 @@
         <v>45835</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32015,7 +32015,7 @@
         <v>45838</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         <v>45848</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32161,7 +32161,7 @@
         <v>45848</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>45857</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>45861</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>45859</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>45866</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>45877</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>45782</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>45891</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>45910</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>46062</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>

--- a/Översikt ÖVERTORNEÅ.xlsx
+++ b/Översikt ÖVERTORNEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45813</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45403</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45705</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45586</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>45784</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>44635</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>45561</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45717</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>46273</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45136</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>45288</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
         <v>45833</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45833</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45127</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>45940</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>46216</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2810,7 +2810,7 @@
         <v>45096</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>46093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>44880</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45446</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45017</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>45985</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>46206</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>46300</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>45044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>44833</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>45462</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>46272</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>46301</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>44833</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>44571</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>44587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>44791</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>46048</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>46171</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>45807</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>45112</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>45425</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>46269</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>45846</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>44585</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>44504</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>44833</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>44494</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>44536</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>44864</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>44536</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>44553</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>44553</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44571</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>44810</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>44497</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>44581</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44553</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>44557</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>44515</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>44757</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>44538</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>44833</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>44687</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>44557</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44551</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>44796</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44692</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44662</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44672</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44585</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>44571</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>44816</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>45673</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>45231</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>44692</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>45136</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>45576</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         <v>45227</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44797</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>45468</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         <v>45554</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>45622</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>45622</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>45377</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         <v>44504</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>44987</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>45142</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         <v>45453</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>45602</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8835,7 +8835,7 @@
         <v>45516</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>45545</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8986,7 +8986,7 @@
         <v>45573</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>45656</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9132,7 +9132,7 @@
         <v>45691</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>45136</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9278,7 +9278,7 @@
         <v>44910</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>44671</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>45194</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9497,7 +9497,7 @@
         <v>44489</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>45274</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>45460</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>45699</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>45395</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>45686</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>44748</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10008,7 +10008,7 @@
         <v>45394</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         <v>45750</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>45633</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>44553</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>45632</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>44904</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10446,7 +10446,7 @@
         <v>45555</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>44911</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>45691</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10665,7 +10665,7 @@
         <v>45460</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10743,7 +10743,7 @@
         <v>45407</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         <v>45390</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>45827</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>45889</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>44860</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>45894</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>45894</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>45127</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>45894</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>45894</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>44589</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>45149</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>46140</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>45899</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>46141</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>46013</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>46057</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>46034</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>45376</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>45908</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>45589</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>45910</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>45537</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>46142</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>45910</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>45633</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>45194</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>45684</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>45919</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>45547</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>45622</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         <v>45621</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13104,7 +13104,7 @@
         <v>45727</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>45729</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>44914</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>45504</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13401,7 +13401,7 @@
         <v>45926</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>45932</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>45932</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>45932</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>45575</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>45936</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>45938</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>45938</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>45938</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         <v>45943</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         <v>45940</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>45601</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>45943</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>45733</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>45946</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>46155</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>45398</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>44729</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>45574</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>45405</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>45959</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>44917</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>44587</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>45451</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45961</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>45965</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15344,7 +15344,7 @@
         <v>45965</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>45965</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>45965</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>45526</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>46160</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>46160</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>45306</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>46163</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
         <v>45978</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>45979</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>45979</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>45979</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>45979</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>45351</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>45118</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>46164</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>46167</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>45743</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>46167</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45985</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45982</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>46167</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>44930</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>46167</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>46035</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>45217</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>46167</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>46167</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>46167</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>45772</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>46167</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45412</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>45857</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>45670</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>45167</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>45960</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>45670</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>45039</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>45995</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>45996</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>45559</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>46003</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>45435</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>46003</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>46008</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>46008</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>46008</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>46008</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>46174</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>46010</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>44529</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>45427</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>45273</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>45848</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>46034</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>46034</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>46034</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>46034</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>46034</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>46032</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>46034</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>46034</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>46178</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>46178</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>46038</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>46038</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20172,7 +20172,7 @@
         <v>46038</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>46038</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>46038</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>46177</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20464,7 +20464,7 @@
         <v>46178</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
         <v>45589</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>46048</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45632</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45632</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>46181</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>45887</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>46183</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>46181</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45405</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>45902</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>45667</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>46056</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>46057</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>46058</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>46059</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>45281</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>46059</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>46062</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>46062</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         <v>45390</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45700</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>46185</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>45460</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         <v>46079</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>46185</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>46080</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>46080</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>45792</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>44776</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22664,7 +22664,7 @@
         <v>46090</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>46094</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>45686</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>46094</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         <v>44589</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>45685</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>46100</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>45622</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>45351</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23321,7 +23321,7 @@
         <v>45953</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23394,7 +23394,7 @@
         <v>44859</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>45104</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23540,7 +23540,7 @@
         <v>46197</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23613,7 +23613,7 @@
         <v>45092</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>45685</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>46124</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>45639</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>45139</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>46132</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>45446</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>45509</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>45449</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45377</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>45188</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>45188</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>45351</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>46162</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>46210</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>44601</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>45757</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>46206</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45870</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>46206</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>45775</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25176,7 +25176,7 @@
         <v>46217</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25249,7 +25249,7 @@
         <v>45574</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25322,7 +25322,7 @@
         <v>46171</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>46136</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25478,7 +25478,7 @@
         <v>45586</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>45579</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>46108</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25697,7 +25697,7 @@
         <v>45329</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>45526</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>46272</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>46231</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25989,7 +25989,7 @@
         <v>45364</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26062,7 +26062,7 @@
         <v>46272</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>45149</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26208,7 +26208,7 @@
         <v>46276</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>46277</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>44923</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26427,7 +26427,7 @@
         <v>46274</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26500,7 +26500,7 @@
         <v>45772</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>45449</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>45632</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>45011</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26792,7 +26792,7 @@
         <v>45112</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>46241</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>46239</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>45602</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>45481</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>46283</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>44532</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>44635</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>46241</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>46094</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>45685</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45561</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>46241</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45136</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>45136</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>46182</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>46246</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>46246</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>46246</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>45117</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>45516</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>45595</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>46293</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>44797</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>46167</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>45017</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45685</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44634</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>44937</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>45515</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>45418</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>45707</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>45727</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>45379</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29279,7 +29279,7 @@
         <v>44672</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>46251</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29430,7 +29430,7 @@
         <v>46251</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>45300</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29581,7 +29581,7 @@
         <v>46301</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>46301</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45629</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45520</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>46301</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>46301</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30019,7 +30019,7 @@
         <v>45705</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30092,7 +30092,7 @@
         <v>45602</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>45526</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30238,7 +30238,7 @@
         <v>46301</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30311,7 +30311,7 @@
         <v>45393</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>46302</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>46304</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>45137</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30603,7 +30603,7 @@
         <v>45222</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30676,7 +30676,7 @@
         <v>45799</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30749,7 +30749,7 @@
         <v>45799</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>46262</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30895,7 +30895,7 @@
         <v>45602</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30968,7 +30968,7 @@
         <v>46265</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31041,7 +31041,7 @@
         <v>46184</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>45139</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>45813</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31265,7 +31265,7 @@
         <v>46269</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>45636</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31416,7 +31416,7 @@
         <v>46311</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>46311</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31562,7 +31562,7 @@
         <v>46267</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31635,7 +31635,7 @@
         <v>46267</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>45826</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31781,7 +31781,7 @@
         <v>45831</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>45835</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31937,7 +31937,7 @@
         <v>45835</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32015,7 +32015,7 @@
         <v>45838</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         <v>45848</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32161,7 +32161,7 @@
         <v>45848</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>45857</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>45861</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>45859</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>45866</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>45877</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>45782</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>45891</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>45910</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>46062</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>

--- a/Översikt ÖVERTORNEÅ.xlsx
+++ b/Översikt ÖVERTORNEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45813</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45403</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45705</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>45586</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>44635</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>45561</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45136</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45833</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>45288</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>46273</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45717</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45833</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45127</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>45096</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>46216</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>45940</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>46093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>44880</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45446</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45017</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>45985</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>46206</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>45044</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>46300</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>44833</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>46301</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>46272</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>45462</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>44833</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>44571</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>44791</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>45112</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>45425</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>46171</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>45807</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>46048</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>45846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>46269</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>44587</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>44585</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>44504</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>44833</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>44494</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>44536</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>44864</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>44536</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>44553</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>44553</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44571</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>44810</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>44497</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>44581</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44553</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>44557</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>44515</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>44757</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>44538</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>44833</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>44687</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>44557</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44551</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>44796</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44692</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44662</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44672</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44585</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>44571</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>44816</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>45827</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>44587</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>45574</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>45281</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>45579</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>45377</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>45329</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>45691</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>45889</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>45894</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>45227</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>45894</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         <v>44860</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>45894</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>45894</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>45390</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>45899</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>45351</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>45231</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         <v>44589</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>45149</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>45772</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>45908</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>45112</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>45910</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>45910</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         <v>44601</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>46163</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>46164</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>46035</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>45670</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>46167</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>45919</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>46167</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>46167</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>45092</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>46167</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>45743</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>46167</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>45670</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>46167</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>46167</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>46167</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>45926</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>45857</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10904,7 +10904,7 @@
         <v>46174</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>45932</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>45932</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>44797</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>45932</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>45936</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>45938</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         <v>45938</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         <v>45938</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
         <v>45136</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         <v>45940</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>45943</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>45943</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>45435</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>45633</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>45127</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>46177</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>45946</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>46178</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45405</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>45574</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>45418</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45887</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>46181</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>46178</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>46181</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>46178</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45902</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>46183</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>46185</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>46185</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
         <v>45633</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>45700</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>45959</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>45961</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>45139</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>45965</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>45965</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>45965</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>45965</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>45379</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>45750</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>46197</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         <v>45953</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>45468</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>45978</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>45979</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>45979</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>45979</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
         <v>45979</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>45982</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>45394</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>45481</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>45707</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>45149</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
         <v>45985</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>45412</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>45960</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>45446</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>45377</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>46210</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15397,7 +15397,7 @@
         <v>45684</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>45039</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>46162</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>46206</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>46206</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>45775</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45306</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
         <v>46136</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>46171</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>45870</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>46217</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>45996</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>45995</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16381,7 +16381,7 @@
         <v>45520</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
         <v>46108</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>46003</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>46003</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>46008</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>46231</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>46008</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>46008</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>46008</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>46010</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>46277</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>45602</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>46239</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>45526</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>45393</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>45848</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>45705</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>46182</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>46241</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>46034</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>46034</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>46034</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>46034</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>46034</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>46032</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18206,7 +18206,7 @@
         <v>46034</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>46034</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18352,7 +18352,7 @@
         <v>46283</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18425,7 +18425,7 @@
         <v>46241</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>46038</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>46038</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>46038</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>46241</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>46038</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>46038</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>45573</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>44635</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>46094</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
         <v>46048</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>45799</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>45136</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>45799</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>45602</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>45137</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19593,7 +19593,7 @@
         <v>45222</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>46246</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>46167</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>46246</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>46056</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>45667</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>46058</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>46246</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45139</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>46057</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>46059</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>46293</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>46062</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>46062</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>46059</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>45813</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>45636</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>46251</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
         <v>45792</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20995,7 +20995,7 @@
         <v>46079</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>45826</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>46080</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>46251</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>46080</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45831</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>45835</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>46090</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>45838</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>45835</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>46094</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>46094</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>46100</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>46302</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>46301</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>46301</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>46301</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         <v>45848</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>45848</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>46301</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>45859</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>45857</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>45861</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>46301</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>45866</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22850,7 +22850,7 @@
         <v>46304</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>46124</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44589</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>45632</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>45877</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>46132</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>45545</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>46265</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>45537</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>45622</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>45622</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>45673</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>46262</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>45300</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>45559</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>46267</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>46267</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>46184</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>45011</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>46311</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>45516</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45351</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45561</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>46269</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>46311</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44923</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>46057</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45376</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24904,7 +24904,7 @@
         <v>46272</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>46013</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>46272</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>45555</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>44910</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>46140</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25342,7 +25342,7 @@
         <v>46274</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>45586</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25488,7 +25488,7 @@
         <v>46142</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>46141</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>46034</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>45554</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>46276</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>46318</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
         <v>45142</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>45460</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>45398</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26155,7 +26155,7 @@
         <v>45217</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26228,7 +26228,7 @@
         <v>44776</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>46155</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>45772</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>45351</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>46160</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>46160</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>44911</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26739,7 +26739,7 @@
         <v>45622</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>45602</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26885,7 +26885,7 @@
         <v>44917</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26958,7 +26958,7 @@
         <v>45407</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27031,7 +27031,7 @@
         <v>45515</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>45427</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27177,7 +27177,7 @@
         <v>45602</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
         <v>45727</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>45656</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>45188</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>44504</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>45685</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>45390</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>45685</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>45273</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45686</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>45686</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>45194</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>44529</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>45526</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>45601</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>45757</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>45117</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45547</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>45632</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>45632</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>45632</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>45575</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>44937</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45104</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44859</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>45364</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>44904</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29148,7 +29148,7 @@
         <v>44532</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29221,7 +29221,7 @@
         <v>45504</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>44930</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>45460</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>45526</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>44987</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>45595</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>45685</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45188</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45449</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>45589</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>45733</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>45118</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>45509</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>45639</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>45629</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>45453</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>44553</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>45727</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>45622</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>45691</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>45621</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30764,7 +30764,7 @@
         <v>44634</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30837,7 +30837,7 @@
         <v>45194</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>45460</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>45516</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>44692</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>44729</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>45699</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>44671</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31358,7 +31358,7 @@
         <v>44672</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
         <v>44748</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>45274</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>44797</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31650,7 +31650,7 @@
         <v>45451</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
         <v>45395</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31796,7 +31796,7 @@
         <v>45017</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>45167</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>45449</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32015,7 +32015,7 @@
         <v>45136</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         <v>45405</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32161,7 +32161,7 @@
         <v>44914</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>45729</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>45685</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>45576</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>45589</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>45782</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45891</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>45910</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>46062</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>

--- a/Översikt ÖVERTORNEÅ.xlsx
+++ b/Översikt ÖVERTORNEÅ.xlsx
@@ -601,7 +601,7 @@
         <v>45813</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>45403</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>45705</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         <v>45705</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>45784</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>45586</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>44635</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         <v>45561</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45136</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>45833</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>45288</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>46273</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>45717</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         <v>45833</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>45889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>45127</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>45096</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>46216</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>45940</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>46093</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>44880</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45446</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>45017</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         <v>45985</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>46206</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>45044</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>46300</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>44833</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>46301</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>46272</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>45462</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>44833</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>44571</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>44791</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>45112</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>45425</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>46171</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>45807</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>46048</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>45846</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>46269</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>44587</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>44585</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>44504</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>44833</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>44494</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5749,7 +5749,7 @@
         <v>44536</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5822,7 +5822,7 @@
         <v>44864</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5895,7 +5895,7 @@
         <v>44536</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>44553</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6041,7 +6041,7 @@
         <v>44553</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>44571</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>44810</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>44497</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>44581</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6411,7 +6411,7 @@
         <v>44553</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6484,7 +6484,7 @@
         <v>44557</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>44515</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>44757</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>44538</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>44833</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>44687</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>44557</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44551</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>44796</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44692</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44662</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44672</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44585</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>44571</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>44816</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>45827</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
         <v>44587</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>45574</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
         <v>45281</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7881,7 +7881,7 @@
         <v>45579</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>45377</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         <v>45329</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>45691</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8173,7 +8173,7 @@
         <v>45889</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         <v>45894</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8324,7 +8324,7 @@
         <v>45227</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>45894</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8475,7 +8475,7 @@
         <v>44860</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>45894</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>45894</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>45390</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>45899</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>45351</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>45231</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         <v>44589</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>45149</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>45772</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9210,7 +9210,7 @@
         <v>45908</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>45112</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>45910</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9429,7 +9429,7 @@
         <v>45910</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         <v>44601</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>46163</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>46164</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>46035</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>45670</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>46167</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>45919</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>46167</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>46167</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10164,7 +10164,7 @@
         <v>45092</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>46167</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>45743</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         <v>46167</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         <v>45670</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>46167</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>46167</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>46167</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         <v>45926</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10831,7 +10831,7 @@
         <v>45857</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10904,7 +10904,7 @@
         <v>46174</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>45932</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>45932</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>44797</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>45932</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>45936</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>45938</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         <v>45938</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         <v>45938</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
         <v>45136</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11654,7 +11654,7 @@
         <v>45940</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>45943</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11805,7 +11805,7 @@
         <v>45943</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         <v>45435</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>45633</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>45127</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>46177</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>45946</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>46178</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45405</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>45574</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>45418</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45887</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>46181</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>46178</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>46181</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>46178</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45902</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>46183</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>46185</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>46185</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
         <v>45633</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>45700</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>45959</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>45961</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>45139</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>45965</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>45965</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>45965</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>45965</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>45379</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>45750</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>46197</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         <v>45953</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>45468</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>45978</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>45979</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>45979</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>45979</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
         <v>45979</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>45982</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>45394</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>45481</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>45707</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>45149</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
         <v>45985</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>45412</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>45960</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>45446</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>45377</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>46210</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15397,7 +15397,7 @@
         <v>45684</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>45039</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15543,7 +15543,7 @@
         <v>46162</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15621,7 +15621,7 @@
         <v>46206</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>46206</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>45775</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45306</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
         <v>46136</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>46171</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>45870</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>46217</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>45996</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>45995</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16381,7 +16381,7 @@
         <v>45520</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
         <v>46108</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>46003</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>46003</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>46008</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>46231</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>46008</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>46008</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>46008</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>46010</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>46277</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>45602</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>46239</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>45526</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>45393</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>45848</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>45705</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>46182</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>46241</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>46034</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>46034</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>46034</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>46034</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18060,7 +18060,7 @@
         <v>46034</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>46032</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18206,7 +18206,7 @@
         <v>46034</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>46034</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18352,7 +18352,7 @@
         <v>46283</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18425,7 +18425,7 @@
         <v>46241</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>46038</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>46038</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18644,7 +18644,7 @@
         <v>46038</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>46241</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>46038</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>46038</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>45573</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>44635</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>46094</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
         <v>46048</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>45799</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>45136</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>45799</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>45602</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>45137</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19593,7 +19593,7 @@
         <v>45222</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>46246</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>46167</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>46246</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>46056</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>45667</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>46058</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>46246</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45139</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>46057</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>46059</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>46293</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>46062</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>46062</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>46059</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>45813</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>45636</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>46251</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
         <v>45792</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20995,7 +20995,7 @@
         <v>46079</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>45826</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>46080</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>46251</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>46080</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45831</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>45835</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>46090</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>45838</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>45835</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>46094</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>46094</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>46100</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>46302</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>46301</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>46301</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>46301</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         <v>45848</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>45848</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>46301</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>45859</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>45857</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>45861</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>46301</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>45866</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22850,7 +22850,7 @@
         <v>46304</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>46124</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>44589</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>45632</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>45877</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23215,7 +23215,7 @@
         <v>46132</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23288,7 +23288,7 @@
         <v>45545</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23366,7 +23366,7 @@
         <v>46265</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>45537</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23512,7 +23512,7 @@
         <v>45622</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>45622</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>45673</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>46262</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>45300</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>45559</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>46267</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24023,7 +24023,7 @@
         <v>46267</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24096,7 +24096,7 @@
         <v>46184</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>45011</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>46311</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24315,7 +24315,7 @@
         <v>45516</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45351</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>45561</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24534,7 +24534,7 @@
         <v>46269</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>46311</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24685,7 +24685,7 @@
         <v>44923</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>46057</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45376</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24904,7 +24904,7 @@
         <v>46272</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>46013</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>46272</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>45555</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>44910</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>46140</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25342,7 +25342,7 @@
         <v>46274</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>45586</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25488,7 +25488,7 @@
         <v>46142</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>46141</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>46034</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>45554</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>46276</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>46318</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
         <v>45142</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>45460</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>45398</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26155,7 +26155,7 @@
         <v>45217</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26228,7 +26228,7 @@
         <v>44776</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>46155</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>45772</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>45351</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>46160</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>46160</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>44911</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26739,7 +26739,7 @@
         <v>45622</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26812,7 +26812,7 @@
         <v>45602</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26885,7 +26885,7 @@
         <v>44917</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26958,7 +26958,7 @@
         <v>45407</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27031,7 +27031,7 @@
         <v>45515</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27104,7 +27104,7 @@
         <v>45427</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27177,7 +27177,7 @@
         <v>45602</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
         <v>45727</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>45656</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>45188</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>44504</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27542,7 +27542,7 @@
         <v>45685</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>45390</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27688,7 +27688,7 @@
         <v>45685</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>45273</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45686</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>45686</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>45194</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>44529</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>45526</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>45601</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>45757</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>45117</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45547</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>45632</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28564,7 +28564,7 @@
         <v>45632</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>45632</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>45575</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>44937</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45104</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44859</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>45364</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>44904</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29148,7 +29148,7 @@
         <v>44532</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29221,7 +29221,7 @@
         <v>45504</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29299,7 +29299,7 @@
         <v>44930</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29372,7 +29372,7 @@
         <v>45460</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29445,7 +29445,7 @@
         <v>45526</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>44987</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>45595</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>45685</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45188</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45449</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>45589</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>45733</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>45118</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>45509</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30180,7 +30180,7 @@
         <v>45639</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>45629</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>45453</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>44553</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>45727</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>45622</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30618,7 +30618,7 @@
         <v>45691</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>45621</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30764,7 +30764,7 @@
         <v>44634</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30837,7 +30837,7 @@
         <v>45194</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>45460</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30988,7 +30988,7 @@
         <v>45516</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31061,7 +31061,7 @@
         <v>44692</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31139,7 +31139,7 @@
         <v>44729</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31212,7 +31212,7 @@
         <v>45699</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>44671</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31358,7 +31358,7 @@
         <v>44672</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31431,7 +31431,7 @@
         <v>44748</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>45274</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>44797</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31650,7 +31650,7 @@
         <v>45451</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
         <v>45395</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31796,7 +31796,7 @@
         <v>45017</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>45167</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>45449</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -32015,7 +32015,7 @@
         <v>45136</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         <v>45405</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32161,7 +32161,7 @@
         <v>44914</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>45729</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>45685</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32380,7 +32380,7 @@
         <v>45576</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32458,7 +32458,7 @@
         <v>45589</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>45782</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45891</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>45910</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32760,7 +32760,7 @@
         <v>46062</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
